--- a/data/nouns.xlsx
+++ b/data/nouns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markjos/projects/tira_parser/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00B0FAF-3E87-4744-8B75-0035077E53F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B280B0E1-63F2-C548-ACF7-F7A0AFBEC4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6701" uniqueCount="2467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6693" uniqueCount="2463">
   <si>
     <t>How to fill in nouns:</t>
   </si>
@@ -7416,18 +7416,12 @@
     <t>beads (PL)</t>
   </si>
   <si>
-    <t>suddenly, quickly, fast (ADV)</t>
-  </si>
-  <si>
     <t>HL</t>
   </si>
   <si>
     <t>tʃútʃù</t>
   </si>
   <si>
-    <t>tʃʊ̀tʃù</t>
-  </si>
-  <si>
     <t>HH20240322</t>
   </si>
   <si>
@@ -7459,12 +7453,6 @@
   </si>
   <si>
     <t>compare to 'suddenly'</t>
-  </si>
-  <si>
-    <t>compare to 'beads'</t>
-  </si>
-  <si>
-    <t>yes (adverb?)</t>
   </si>
   <si>
     <t>?(H)H</t>
@@ -9037,7 +9025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG995"/>
+  <dimension ref="A1:AG994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9.6640625" customWidth="1"/>
@@ -15498,7 +15486,7 @@
         <v>662</v>
       </c>
       <c r="J133" s="14" t="s">
-        <v>2458</v>
+        <v>2454</v>
       </c>
       <c r="K133" s="14" t="s">
         <v>2172</v>
@@ -15581,7 +15569,7 @@
         <v>93</v>
       </c>
       <c r="J134" s="14" t="s">
-        <v>2459</v>
+        <v>2455</v>
       </c>
       <c r="K134" s="14" t="s">
         <v>1782</v>
@@ -15670,7 +15658,7 @@
         <v>639</v>
       </c>
       <c r="J135" s="14" t="s">
-        <v>2459</v>
+        <v>2455</v>
       </c>
       <c r="K135" s="14" t="s">
         <v>2182</v>
@@ -15759,10 +15747,10 @@
         <v>627</v>
       </c>
       <c r="J136" s="14" t="s">
-        <v>2460</v>
+        <v>2456</v>
       </c>
       <c r="K136" s="14" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="L136" s="14" t="s">
         <v>803</v>
@@ -15791,7 +15779,7 @@
         <v>644</v>
       </c>
       <c r="V136" s="14" t="s">
-        <v>2466</v>
+        <v>2462</v>
       </c>
       <c r="W136" s="14" t="s">
         <v>805</v>
@@ -15840,7 +15828,7 @@
         <v>662</v>
       </c>
       <c r="J137" s="14" t="s">
-        <v>2461</v>
+        <v>2457</v>
       </c>
       <c r="K137" s="14" t="s">
         <v>2197</v>
@@ -15921,47 +15909,47 @@
         <v>662</v>
       </c>
       <c r="J138" s="14" t="s">
-        <v>2462</v>
+        <v>2458</v>
       </c>
       <c r="K138" s="14" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
       <c r="L138" s="14" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="M138" s="14"/>
       <c r="N138" s="14"/>
       <c r="O138" s="15" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
       <c r="P138" s="15" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="Q138" s="15"/>
       <c r="R138" s="14" t="s">
-        <v>2453</v>
+        <v>2451</v>
       </c>
       <c r="S138" s="14" t="s">
         <v>643</v>
       </c>
       <c r="T138" s="14" t="s">
-        <v>2451</v>
+        <v>2449</v>
       </c>
       <c r="U138" s="14" t="s">
         <v>633</v>
       </c>
       <c r="V138" s="14" t="s">
-        <v>2452</v>
+        <v>2450</v>
       </c>
       <c r="W138" s="14" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
       <c r="X138" s="14"/>
       <c r="Y138" s="15" t="s">
-        <v>2454</v>
+        <v>2452</v>
       </c>
       <c r="Z138" s="15" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
       <c r="AA138" s="15"/>
       <c r="AB138" s="14"/>
@@ -17280,7 +17268,7 @@
         <v>100</v>
       </c>
       <c r="V153" s="14" t="s">
-        <v>2463</v>
+        <v>2459</v>
       </c>
       <c r="W153" s="14" t="s">
         <v>632</v>
@@ -17289,7 +17277,7 @@
         <v>563</v>
       </c>
       <c r="Y153" s="15" t="s">
-        <v>2464</v>
+        <v>2460</v>
       </c>
       <c r="Z153" s="15" t="s">
         <v>632</v>
@@ -17821,7 +17809,7 @@
         <v>563</v>
       </c>
       <c r="Y159" s="15" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="Z159" s="15" t="s">
         <v>666</v>
@@ -21130,7 +21118,7 @@
         <v>662</v>
       </c>
       <c r="J197" s="14" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="K197" s="14" t="s">
         <v>732</v>
@@ -21229,7 +21217,7 @@
         <v>707</v>
       </c>
       <c r="J198" s="14" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="K198" s="14" t="s">
         <v>752</v>
@@ -21328,7 +21316,7 @@
         <v>93</v>
       </c>
       <c r="J199" s="19" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="K199" s="14" t="s">
         <v>761</v>
@@ -21415,7 +21403,7 @@
         <v>639</v>
       </c>
       <c r="J200" s="14" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="K200" s="14" t="s">
         <v>744</v>
@@ -21496,19 +21484,19 @@
       </c>
       <c r="G201" s="12"/>
       <c r="H201" s="12" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
       <c r="I201" s="13" t="s">
         <v>1324</v>
       </c>
       <c r="J201" s="14" t="s">
+        <v>2441</v>
+      </c>
+      <c r="K201" s="14" t="s">
         <v>2442</v>
       </c>
-      <c r="K201" s="14" t="s">
+      <c r="L201" s="14" t="s">
         <v>2443</v>
-      </c>
-      <c r="L201" s="14" t="s">
-        <v>2445</v>
       </c>
       <c r="M201" s="14"/>
       <c r="N201" s="14"/>
@@ -21524,10 +21512,10 @@
       <c r="T201" s="14"/>
       <c r="U201" s="14"/>
       <c r="V201" s="14" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="W201" s="14" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="X201" s="14"/>
       <c r="Y201" s="15"/>
@@ -34680,34 +34668,18 @@
       <c r="AG350" s="15"/>
     </row>
     <row r="351" spans="1:33" ht="15.75" customHeight="1">
-      <c r="A351" s="10" t="s">
-        <v>2438</v>
-      </c>
+      <c r="A351" s="10"/>
       <c r="B351" s="10"/>
       <c r="C351" s="11"/>
       <c r="D351" s="11"/>
-      <c r="E351" s="11" t="s">
-        <v>2441</v>
-      </c>
-      <c r="F351" s="12" t="s">
-        <v>2457</v>
-      </c>
+      <c r="E351" s="11"/>
+      <c r="F351" s="12"/>
       <c r="G351" s="12"/>
-      <c r="H351" s="12" t="s">
-        <v>2456</v>
-      </c>
-      <c r="I351" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="J351" s="14" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K351" s="14" t="s">
-        <v>2444</v>
-      </c>
-      <c r="L351" s="14" t="s">
-        <v>2445</v>
-      </c>
+      <c r="H351" s="12"/>
+      <c r="I351" s="13"/>
+      <c r="J351" s="14"/>
+      <c r="K351" s="14"/>
+      <c r="L351" s="14"/>
       <c r="M351" s="14"/>
       <c r="N351" s="14"/>
       <c r="O351" s="15"/>
@@ -56745,15 +56717,15 @@
       <c r="AF980" s="15"/>
       <c r="AG980" s="15"/>
     </row>
-    <row r="981" spans="1:33" ht="15.75" customHeight="1">
+    <row r="981" spans="1:33" ht="15" customHeight="1">
       <c r="A981" s="10"/>
       <c r="B981" s="10"/>
       <c r="C981" s="11"/>
       <c r="D981" s="11"/>
       <c r="E981" s="11"/>
-      <c r="F981" s="12"/>
-      <c r="G981" s="12"/>
-      <c r="H981" s="12"/>
+      <c r="F981" s="28"/>
+      <c r="G981" s="28"/>
+      <c r="H981" s="28"/>
       <c r="I981" s="13"/>
       <c r="J981" s="14"/>
       <c r="K981" s="14"/>
@@ -56771,8 +56743,6 @@
       <c r="W981" s="14"/>
       <c r="X981" s="14"/>
       <c r="Y981" s="15"/>
-      <c r="Z981" s="15"/>
-      <c r="AA981" s="15"/>
       <c r="AB981" s="14"/>
       <c r="AC981" s="14"/>
       <c r="AD981" s="14"/>
@@ -56780,38 +56750,12 @@
       <c r="AF981" s="15"/>
       <c r="AG981" s="15"/>
     </row>
-    <row r="982" spans="1:33" ht="15" customHeight="1">
+    <row r="982" spans="1:33" ht="16">
       <c r="A982" s="10"/>
       <c r="B982" s="10"/>
-      <c r="C982" s="11"/>
-      <c r="D982" s="11"/>
-      <c r="E982" s="11"/>
       <c r="F982" s="28"/>
       <c r="G982" s="28"/>
       <c r="H982" s="28"/>
-      <c r="I982" s="13"/>
-      <c r="J982" s="14"/>
-      <c r="K982" s="14"/>
-      <c r="L982" s="14"/>
-      <c r="M982" s="14"/>
-      <c r="N982" s="14"/>
-      <c r="O982" s="15"/>
-      <c r="P982" s="15"/>
-      <c r="Q982" s="15"/>
-      <c r="R982" s="14"/>
-      <c r="S982" s="14"/>
-      <c r="T982" s="14"/>
-      <c r="U982" s="14"/>
-      <c r="V982" s="14"/>
-      <c r="W982" s="14"/>
-      <c r="X982" s="14"/>
-      <c r="Y982" s="15"/>
-      <c r="AB982" s="14"/>
-      <c r="AC982" s="14"/>
-      <c r="AD982" s="14"/>
-      <c r="AE982" s="15"/>
-      <c r="AF982" s="15"/>
-      <c r="AG982" s="15"/>
     </row>
     <row r="983" spans="1:33" ht="16">
       <c r="A983" s="10"/>
@@ -56897,17 +56841,10 @@
       <c r="G994" s="28"/>
       <c r="H994" s="28"/>
     </row>
-    <row r="995" spans="1:8" ht="16">
-      <c r="A995" s="10"/>
-      <c r="B995" s="10"/>
-      <c r="F995" s="28"/>
-      <c r="G995" s="28"/>
-      <c r="H995" s="28"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG351">
-    <sortCondition ref="F2:F351"/>
-    <sortCondition ref="J2:J351"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AG350">
+    <sortCondition ref="F2:F350"/>
+    <sortCondition ref="J2:J350"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="L144" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
